--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9AB91A-E937-487C-BB23-35AE2D2E1D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7493B8B6-9DE3-4196-A485-AA650AA2D5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="4425" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,6 +90,22 @@
   </si>
   <si>
     <t>不知名的病例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午睡，尽力地多睡点，中间断开时候感觉到剧烈的头疼。我尝试关注它，但是逃走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上时候睡眠中断了，因为窗帘没有拉上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠债务缓和些许</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 1 勺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,8 +450,9 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
@@ -503,11 +520,21 @@
       <c r="A3" s="3">
         <v>46105</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2">
+        <v>6</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7493B8B6-9DE3-4196-A485-AA650AA2D5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779DE27B-A3FF-4936-BA9E-719EC0AFD01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,17 @@
   </si>
   <si>
     <t>硫辛酸 1 勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 2 勺</t>
+  </si>
+  <si>
+    <t>30分钟的午睡，很困，但是没有后续反应。我睡不着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>似乎很晚睡着，总之是一直在黑暗中躺着</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,11 +557,21 @@
       <c r="A4" s="3">
         <v>46106</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779DE27B-A3FF-4936-BA9E-719EC0AFD01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13EC7D1-CECC-49C4-9104-5DEA9EC2CA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="4650" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -117,6 +117,26 @@
   </si>
   <si>
     <t>似乎很晚睡着，总之是一直在黑暗中躺着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身体上有着严重的疲劳，躺在床上感觉背部很痛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡觉债务基本清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>似乎睡得很晚，但是早上做了梦，梦见高考模拟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天下午尝试午睡，但是是间断的，焦躁的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -467,6 +487,7 @@
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -494,7 +515,9 @@
       <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J1" s="4" t="s">
         <v>10</v>
       </c>
@@ -574,7 +597,9 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -583,11 +608,19 @@
       <c r="A5" s="3">
         <v>46107</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2">
+        <v>6</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13EC7D1-CECC-49C4-9104-5DEA9EC2CA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB28D7E1-DB80-425D-A975-E4FA577B119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="4650" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +137,26 @@
   </si>
   <si>
     <t>今天下午尝试午睡，但是是间断的，焦躁的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨晚大约一点睡觉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠债务扩表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试睡午觉，很困</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能睡得更多了，八点就醒了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无事发生</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,12 +183,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -183,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -196,6 +222,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,11 +658,19 @@
       <c r="A6" s="3">
         <v>46108</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -642,11 +679,17 @@
       <c r="A7" s="3">
         <v>46109</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5">
+        <v>6</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -655,11 +698,11 @@
       <c r="A8" s="3">
         <v>46110</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB28D7E1-DB80-425D-A975-E4FA577B119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8415583-C61E-4E40-A4E5-14CD3E949887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8595" yWindow="4575" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +157,26 @@
   </si>
   <si>
     <t>无事发生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>半夜被蚊子咬醒了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上没有睡着睡晚了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>半夜被热醒，被蚊子咬醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 5 勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡午觉，睡过头了。大抵是睡了两个小时的样子。硫辛酸似乎对睡眠不足的头疼有效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -220,11 +240,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,11 +567,11 @@
       <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
@@ -575,9 +595,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
@@ -601,9 +621,9 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
@@ -629,9 +649,9 @@
       <c r="I4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -679,15 +699,15 @@
       <c r="A7" s="3">
         <v>46109</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>6</v>
       </c>
       <c r="G7" s="2"/>
@@ -698,11 +718,17 @@
       <c r="A8" s="3">
         <v>46110</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -712,10 +738,16 @@
         <v>46111</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -725,10 +757,18 @@
         <v>46112</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -740,7 +780,6 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8415583-C61E-4E40-A4E5-14CD3E949887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EAB019-EBAA-414F-BAE7-ED97C3BED4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="4575" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,6 +177,14 @@
   </si>
   <si>
     <t>睡午觉，睡过头了。大抵是睡了两个小时的样子。硫辛酸似乎对睡眠不足的头疼有效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不错的睡眠，就是总时间少了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有睡够，装了风扇感到凉快</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +205,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -212,7 +228,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -229,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -243,14 +259,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -261,6 +288,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:I49" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:I49" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况"/>
+    <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）"/>
+    <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为"/>
+    <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物"/>
+    <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数"/>
+    <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例"/>
+    <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述"/>
+    <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -534,8 +579,9 @@
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="10.25" customWidth="1"/>
     <col min="9" max="9" width="44.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -567,11 +613,6 @@
       <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
@@ -595,9 +636,6 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
@@ -621,9 +659,6 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
@@ -649,9 +684,6 @@
       <c r="I4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -673,6 +705,11 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
+      <c r="J5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -694,6 +731,9 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -713,25 +753,31 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>46110</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
         <v>4</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -741,7 +787,7 @@
       <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="2"/>
@@ -778,9 +824,13 @@
         <v>46113</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2">
+        <v>6</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -790,10 +840,14 @@
         <v>46114</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>7</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2201,9 +2255,12 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:L4"/>
+    <mergeCell ref="J5:L8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EAB019-EBAA-414F-BAE7-ED97C3BED4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95606347-3C20-4D69-951E-74F5B454ED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -185,6 +185,41 @@
   </si>
   <si>
     <t>没有睡够，装了风扇感到凉快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还算完整的睡眠 睡眠时数在八小时以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>想要赖床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位于鼻腔下沿靠近喉咙的位置感到有异物，有东西卡在上面。可能是烟雾带来的过敏</t>
+  </si>
+  <si>
+    <t>鼻腔下沿的疼痛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天早上好些许，至少不会痛了。晚上时候流鼻涕了。很可能和感冒相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感冒，来源等待确认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡饱饱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流鼻涕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能不是感冒，和也可能是细菌性感冒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -245,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -259,22 +294,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -291,10 +333,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:I49" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:I49" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:I100" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I100" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况"/>
     <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）"/>
     <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为"/>
@@ -304,7 +346,7 @@
     <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述"/>
     <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -580,8 +622,8 @@
     <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -705,11 +747,11 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -731,9 +773,9 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -753,9 +795,9 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -775,9 +817,9 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -794,8 +836,8 @@
       <c r="F9" s="2">
         <v>5</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -815,8 +857,8 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -831,8 +873,8 @@
       <c r="F11" s="2">
         <v>6</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -856,134 +898,187 @@
       <c r="A13" s="3">
         <v>46115</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="2">
+        <v>7</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>46116</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>46117</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>46118</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="9"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>46119</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="9"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>46120</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="9"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>46121</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="9"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>46122</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>46123</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>46124</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>46125</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>46126</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>46127</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46128</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>46132</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>46133</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>46134</v>
       </c>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95606347-3C20-4D69-951E-74F5B454ED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE1A5AA-BC1C-4561-9CF1-779DCE97E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,7 +219,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可能不是感冒，和也可能是细菌性感冒</t>
+    <t>晚上被蚊子咬醒，早上被铃声吵醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大概率是感冒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能不是感冒，和可能是细菌性感冒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还有些鼻塞，鼻涕不怎么流。鼻腔痒痒的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -300,13 +312,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -747,11 +759,11 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -773,9 +785,9 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -795,9 +807,9 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -817,9 +829,9 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -898,12 +910,12 @@
       <c r="A13" s="3">
         <v>46115</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="2">
         <v>7</v>
       </c>
@@ -918,12 +930,12 @@
       <c r="A14" s="3">
         <v>46116</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2">
         <v>7</v>
       </c>
@@ -938,12 +950,12 @@
       <c r="A15" s="3">
         <v>46117</v>
       </c>
-      <c r="B15" s="9"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="9"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="2">
         <v>8</v>
       </c>
@@ -951,29 +963,37 @@
         <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>46118</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>46119</v>
       </c>
-      <c r="B17" s="9"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="2"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -982,11 +1002,11 @@
       <c r="A18" s="3">
         <v>46120</v>
       </c>
-      <c r="B18" s="9"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
@@ -994,11 +1014,11 @@
       <c r="A19" s="3">
         <v>46121</v>
       </c>
-      <c r="B19" s="9"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
@@ -1006,11 +1026,11 @@
       <c r="A20" s="3">
         <v>46122</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
@@ -1018,11 +1038,11 @@
       <c r="A21" s="3">
         <v>46123</v>
       </c>
-      <c r="B21" s="9"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE1A5AA-BC1C-4561-9CF1-779DCE97E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7B9BC2-4F1F-499F-AADA-59F6E09E49E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="34110" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -232,6 +232,22 @@
   </si>
   <si>
     <t>还有些鼻塞，鼻涕不怎么流。鼻腔痒痒的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上睡得迟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失眠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 4 勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午尝试睡觉，非常严重的睡意，但是没有睡着。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -991,10 +1007,14 @@
         <v>46119</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2">
+        <v>6</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
@@ -1003,10 +1023,16 @@
         <v>46120</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
@@ -1015,10 +1041,18 @@
         <v>46121</v>
       </c>
       <c r="B19" s="7"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
@@ -1029,8 +1063,8 @@
       <c r="B20" s="7"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
@@ -1041,8 +1075,8 @@
       <c r="B21" s="7"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
@@ -1050,6 +1084,8 @@
       <c r="A22" s="3">
         <v>46124</v>
       </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
@@ -1057,6 +1093,8 @@
       <c r="A23" s="3">
         <v>46125</v>
       </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7B9BC2-4F1F-499F-AADA-59F6E09E49E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426C6704-CA52-4510-A9FC-F5661C86B259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="34110" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="4815" windowWidth="34110" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -248,6 +248,26 @@
   </si>
   <si>
     <t>中午尝试睡觉，非常严重的睡意，但是没有睡着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午昏迷了一小会，但是没有睡着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠开始于两点，结束于八点半</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠仍旧不足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午睡没有睡着，尝试运行想象，但是被疼痛击退了，想象事物伴随着疼痛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不知睡眠从何处开始，睡眠结束于八点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -358,6 +378,901 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.8997642437127032E-2"/>
+          <c:y val="0.12161185734136173"/>
+          <c:w val="0.89655796150481193"/>
+          <c:h val="0.65716025080198304"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-5122-4334-A63D-F057C7439F74}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1222332576"/>
+        <c:axId val="1222331616"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1222332576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1222331616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1222331616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1222332576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>528637</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>5095875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD88DABC-9120-5CD2-2976-6CB18E6C4B89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,7 +1565,7 @@
     <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5" customWidth="1"/>
-    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="77.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -926,7 +1841,7 @@
       <c r="A13" s="3">
         <v>46115</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
@@ -946,7 +1861,7 @@
       <c r="A14" s="3">
         <v>46116</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
@@ -966,7 +1881,7 @@
       <c r="A15" s="3">
         <v>46117</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>43</v>
       </c>
@@ -986,7 +1901,7 @@
       <c r="A16" s="3">
         <v>46118</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1006,7 +1921,7 @@
       <c r="A17" s="3">
         <v>46119</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1022,7 +1937,7 @@
       <c r="A18" s="3">
         <v>46120</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1040,7 +1955,7 @@
       <c r="A19" s="3">
         <v>46121</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
         <v>50</v>
       </c>
@@ -1060,11 +1975,17 @@
       <c r="A20" s="3">
         <v>46122</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
@@ -1072,11 +1993,15 @@
       <c r="A21" s="3">
         <v>46123</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
@@ -1084,8 +2009,14 @@
       <c r="A22" s="3">
         <v>46124</v>
       </c>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
@@ -1093,48 +2024,88 @@
       <c r="A23" s="3">
         <v>46125</v>
       </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>46126</v>
       </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>46127</v>
       </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46128</v>
       </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46129</v>
       </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46130</v>
       </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>46131</v>
       </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>46132</v>
       </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>46133</v>
       </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
@@ -2412,8 +3383,9 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426C6704-CA52-4510-A9FC-F5661C86B259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00789707-0FC2-410D-9796-5D95022019AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4815" windowWidth="34110" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -268,6 +268,22 @@
   </si>
   <si>
     <t>不知睡眠从何处开始，睡眠结束于八点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠不足，但是症状少了些</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昏迷般的午睡，没有睡着。今天在听课时候感到大脑发痛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠不足，症状并不少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有睡着的午觉，但是想要继续睡觉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -509,6 +525,12 @@
                 <c:pt idx="21">
                   <c:v>5</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -692,13 +714,10 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -2042,10 +2061,16 @@
         <v>46126</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -2053,10 +2078,16 @@
         <v>46127</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="2">
+        <v>3</v>
+      </c>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00789707-0FC2-410D-9796-5D95022019AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7445592F-45F9-4905-AE77-D0777CF64C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -284,6 +284,22 @@
   </si>
   <si>
     <t>没有睡着的午觉，但是想要继续睡觉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上四点的时候被蚊子咬醒了，但是今天以外的没有困意</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午觉没有睡着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强行睡到了九点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡得不算安慰，好歹是睡了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -530,6 +546,15 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,7 +1605,7 @@
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5" customWidth="1"/>
@@ -1885,7 +1910,7 @@
         <v>37</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2">
         <v>7</v>
       </c>
@@ -1905,7 +1930,7 @@
         <v>43</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2">
         <v>8</v>
       </c>
@@ -1925,7 +1950,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2">
         <v>5</v>
       </c>
@@ -1945,7 +1970,7 @@
         <v>49</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2">
         <v>6</v>
       </c>
@@ -2055,6 +2080,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
@@ -2072,6 +2098,7 @@
         <v>4</v>
       </c>
       <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
@@ -2089,14 +2116,25 @@
         <v>3</v>
       </c>
       <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46128</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
@@ -2105,22 +2143,42 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46130</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>46131</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
@@ -2129,6 +2187,10 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
@@ -2137,88 +2199,152 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>46134</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>46135</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>46136</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>46137</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>46138</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>46139</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>46140</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>46141</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>46142</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>46143</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>46144</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>46145</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>46146</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>46147</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>46148</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46149</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46150</v>
       </c>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7445592F-45F9-4905-AE77-D0777CF64C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EF3656-FDE1-40AE-93A0-DC0726E3FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,6 +300,22 @@
   </si>
   <si>
     <t>睡得不算安慰，好歹是睡了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不得不回忆起睡眠时间守恒的理论，困倦但是睡不着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午睡两小时，但是午睡没有睡着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">感觉自己要死了，最好天上、掉下来写什么把我砸到一觉不醒 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困倦，但程度比昨天要少</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -433,8 +449,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.8997642437127032E-2"/>
-          <c:y val="0.12161185734136173"/>
+          <c:x val="5.3436234328055603E-2"/>
+          <c:y val="0.1216119413644723"/>
           <c:w val="0.89655796150481193"/>
           <c:h val="0.65716025080198304"/>
         </c:manualLayout>
@@ -556,6 +572,18 @@
                 <c:pt idx="27">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -563,6 +591,344 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-5122-4334-A63D-F057C7439F74}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1222332576"/>
+        <c:axId val="1222331616"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1222332576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1222331616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1222331616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1222332576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3436234328055603E-2"/>
+          <c:y val="5.8119877872408805E-2"/>
+          <c:w val="0.89655796150481193"/>
+          <c:h val="0.65716025080198304"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-549F-4933-B255-EE02814AB3E0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -775,6 +1141,43 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -1278,20 +1681,523 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>528637</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>347662</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>5095875</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>3448050</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1311,6 +2217,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3538538</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65781FE9-F6ED-47A9-84DB-0134B85BF738}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2185,10 +3129,18 @@
         <v>46132</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
@@ -2200,7 +3152,9 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2">
+        <v>4</v>
+      </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
@@ -2208,10 +3162,16 @@
       <c r="A32" s="3">
         <v>46134</v>
       </c>
-      <c r="C32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
@@ -2219,10 +3179,16 @@
       <c r="A33" s="3">
         <v>46135</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="2">
+        <v>4</v>
+      </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EF3656-FDE1-40AE-93A0-DC0726E3FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB70A74-FCCA-488D-A50E-64AF0A2CD24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -316,6 +316,14 @@
   </si>
   <si>
     <t>困倦，但程度比昨天要少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有睡饱，明明是周末的说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能更早的时候醒了，总之今天睡觉睡到了10点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,6 +590,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -920,6 +931,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -3196,10 +3210,16 @@
       <c r="A34" s="3">
         <v>46136</v>
       </c>
-      <c r="C34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="2">
+        <v>4</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
@@ -3207,10 +3227,14 @@
       <c r="A35" s="3">
         <v>46137</v>
       </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="F35" s="2">
+        <v>6</v>
+      </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB70A74-FCCA-488D-A50E-64AF0A2CD24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD8EA72-CC4D-4A95-928A-C5B7321D5CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="675" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -311,10 +311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">感觉自己要死了，最好天上、掉下来写什么把我砸到一觉不醒 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>困倦，但程度比昨天要少</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,6 +320,34 @@
   </si>
   <si>
     <t>可能更早的时候醒了，总之今天睡觉睡到了10点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡得不够多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困倦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困倦，晚上做恶梦，睡得更少了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9点时候喝咖啡，效果持续了一个小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">感觉自己要死了，最好天上、掉下来些什么把我砸到一觉不醒 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -358,7 +382,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +392,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -405,6 +435,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -495,10 +528,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$34</c:f>
+              <c:f>Sheet1!$H$2:$H$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -518,7 +551,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5</c:v>
@@ -592,7 +625,19 @@
                 <c:pt idx="31">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -836,10 +881,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$34</c:f>
+              <c:f>Sheet1!$H$2:$H$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -859,7 +904,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5</c:v>
@@ -933,7 +978,7 @@
                 <c:pt idx="31">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -2202,13 +2247,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>347662</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>3448050</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2238,13 +2283,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>3538538</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -2278,14 +2323,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:I100" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I100" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:K100" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:K100" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况"/>
     <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）"/>
     <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为"/>
     <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物"/>
+    <tableColumn id="11" xr3:uid="{7B1284C1-BD4F-40C2-8A90-EA6374B9CCBF}" name="B"/>
+    <tableColumn id="12" xr3:uid="{4889870D-81B3-48E8-8B32-09DEA589C185}" name="C"/>
     <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数"/>
     <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例"/>
     <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述"/>
@@ -2558,21 +2605,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:N285"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="79.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5" customWidth="1"/>
-    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="77.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.5" customWidth="1"/>
+    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2589,19 +2636,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>46104</v>
       </c>
@@ -2617,14 +2670,16 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>46105</v>
       </c>
@@ -2640,14 +2695,16 @@
       <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2">
         <v>6</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>46106</v>
       </c>
@@ -2663,16 +2720,18 @@
       <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>6</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>46107</v>
       </c>
@@ -2686,19 +2745,21 @@
         <v>24</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>6</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>46108</v>
       </c>
@@ -2712,17 +2773,19 @@
         <v>27</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>46109</v>
       </c>
@@ -2734,17 +2797,19 @@
         <v>29</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>6</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>46110</v>
       </c>
@@ -2756,17 +2821,19 @@
         <v>29</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <v>4</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="4">
+        <v>6</v>
+      </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>46111</v>
       </c>
@@ -2778,14 +2845,16 @@
         <v>29</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>46112</v>
       </c>
@@ -2799,14 +2868,16 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>46113</v>
       </c>
@@ -2815,14 +2886,14 @@
         <v>35</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="F11" s="2">
+      <c r="H11" s="2">
         <v>6</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>46114</v>
       </c>
@@ -2832,14 +2903,16 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2">
         <v>7</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>46115</v>
       </c>
@@ -2849,17 +2922,19 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="2">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="2">
         <v>7</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>46116</v>
       </c>
@@ -2869,17 +2944,19 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2">
         <v>7</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="J14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>46117</v>
       </c>
@@ -2889,17 +2966,19 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
         <v>8</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>46118</v>
       </c>
@@ -2909,17 +2988,19 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2">
         <v>5</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>46119</v>
       </c>
@@ -2929,13 +3010,15 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
         <v>6</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>46120</v>
       </c>
@@ -2947,13 +3030,15 @@
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2">
         <v>5</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>46121</v>
       </c>
@@ -2967,13 +3052,15 @@
       <c r="E19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
         <v>3</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>46122</v>
       </c>
@@ -2985,13 +3072,15 @@
         <v>53</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>46123</v>
       </c>
@@ -3001,13 +3090,15 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2">
         <v>4</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>46124</v>
       </c>
@@ -3016,13 +3107,15 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2">
         <v>4</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>46125</v>
       </c>
@@ -3034,13 +3127,15 @@
         <v>56</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2">
         <v>5</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>46126</v>
       </c>
@@ -3052,13 +3147,15 @@
         <v>59</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>46127</v>
       </c>
@@ -3070,13 +3167,15 @@
         <v>61</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2">
         <v>3</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46128</v>
       </c>
@@ -3088,13 +3187,15 @@
         <v>63</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2">
         <v>5</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46129</v>
       </c>
@@ -3105,8 +3206,10 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46130</v>
       </c>
@@ -3116,13 +3219,15 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2">
         <v>6</v>
       </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>46131</v>
       </c>
@@ -3132,13 +3237,15 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2">
         <v>6</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>46132</v>
       </c>
@@ -3152,13 +3259,15 @@
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>46133</v>
       </c>
@@ -3166,123 +3275,149 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
         <v>4</v>
       </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>46134</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>46135</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2">
         <v>4</v>
       </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>46136</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="2">
-        <v>4</v>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>46137</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2">
-        <v>6</v>
-      </c>
+      <c r="E35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H35" s="2">
+        <v>4</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>46138</v>
       </c>
-      <c r="C36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H36" s="2">
+        <v>6</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>46139</v>
       </c>
-      <c r="C37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="2">
+        <v>5</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>46140</v>
       </c>
-      <c r="C38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H38" s="2">
+        <v>4</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>46141</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="C39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H39" s="2">
+        <v>4</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>46142</v>
       </c>
@@ -3292,8 +3427,10 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>46143</v>
       </c>
@@ -3303,38 +3440,40 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>46144</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>46145</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>46146</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>46147</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>46148</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46149</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46150</v>
       </c>
@@ -4526,7 +4665,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J5:L8"/>
+    <mergeCell ref="L5:N8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD8EA72-CC4D-4A95-928A-C5B7321D5CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24159E2-AFF5-4BF2-9BCB-7C3EED6EE40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="675" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -348,6 +348,34 @@
   </si>
   <si>
     <t xml:space="preserve">感觉自己要死了，最好天上、掉下来些什么把我砸到一觉不醒 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头疼，晚上有人打呼噜，大致是晚上两点睡觉的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上吃抹茶，看起来没有效果，中午吃了对乙酰氨基酚，头不痛很有精神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨晚睡得实在是太晚了，聊天聊多了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尽力睡觉了，但是不够睡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡饱了，但是起床是10点整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起床是10点整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上两点睡觉，起床是11点整，做了不错的梦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,6 +667,24 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3421,12 +3467,20 @@
       <c r="A40" s="3">
         <v>46142</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="C40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
+      <c r="H40" s="2">
+        <v>3</v>
+      </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
@@ -3434,12 +3488,18 @@
       <c r="A41" s="3">
         <v>46143</v>
       </c>
-      <c r="C41" s="2"/>
+      <c r="C41" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
+      <c r="H41" s="2">
+        <v>4</v>
+      </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
@@ -3447,113 +3507,171 @@
       <c r="A42" s="3">
         <v>46144</v>
       </c>
+      <c r="C42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="2">
+        <v>5</v>
+      </c>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>46145</v>
       </c>
+      <c r="C43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H43" s="2">
+        <v>6</v>
+      </c>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>46146</v>
       </c>
+      <c r="C44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="2">
+        <v>6</v>
+      </c>
+      <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>46147</v>
       </c>
+      <c r="C45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H45" s="2">
+        <v>6</v>
+      </c>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>46148</v>
       </c>
+      <c r="C46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46149</v>
       </c>
+      <c r="C47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46150</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>46151</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>46152</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>46153</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>46154</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>46155</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="C53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>46156</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>46157</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>46158</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>46159</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>46160</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>46161</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>46162</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>46163</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>46164</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>46165</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>46166</v>
       </c>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24159E2-AFF5-4BF2-9BCB-7C3EED6EE40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196A9848-7FB3-4CA0-AF18-73ED00F16F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,6 +376,26 @@
   </si>
   <si>
     <t>晚上两点睡觉，起床是11点整，做了不错的梦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很迟的睡眠，拼尽全力无法睡够</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡眠稀少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困得要死，甚至滑行过了早上的铃声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 1 勺，瓜拉纳2勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午睡，但是清醒梦，精力吃光光</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -685,6 +705,12 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3510,6 +3536,7 @@
       <c r="C42" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="D42" s="2"/>
       <c r="E42" s="2" t="s">
         <v>16</v>
       </c>
@@ -3526,6 +3553,7 @@
       <c r="C43" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="D43" s="2"/>
       <c r="H43" s="2">
         <v>6</v>
       </c>
@@ -3538,6 +3566,7 @@
       <c r="C44" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="D44" s="2"/>
       <c r="H44" s="2">
         <v>6</v>
       </c>
@@ -3550,6 +3579,7 @@
       <c r="C45" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="D45" s="2"/>
       <c r="H45" s="2">
         <v>6</v>
       </c>
@@ -3559,23 +3589,47 @@
       <c r="A46" s="3">
         <v>46148</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="C46" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="2">
+        <v>4</v>
+      </c>
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46149</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="C47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="2">
+        <v>3</v>
+      </c>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46150</v>
       </c>
-      <c r="C48" s="2"/>
+      <c r="C48" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
     </row>
@@ -3584,6 +3638,7 @@
         <v>46151</v>
       </c>
       <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
@@ -3592,6 +3647,7 @@
         <v>46152</v>
       </c>
       <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
@@ -3600,6 +3656,7 @@
         <v>46153</v>
       </c>
       <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
     </row>
@@ -3608,6 +3665,7 @@
         <v>46154</v>
       </c>
       <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
     </row>
@@ -3616,6 +3674,7 @@
         <v>46155</v>
       </c>
       <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
     </row>
@@ -3623,6 +3682,7 @@
       <c r="A54" s="3">
         <v>46156</v>
       </c>
+      <c r="D54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
     </row>
@@ -3630,6 +3690,7 @@
       <c r="A55" s="3">
         <v>46157</v>
       </c>
+      <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196A9848-7FB3-4CA0-AF18-73ED00F16F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD52ECF-EB77-414A-B651-840CA0D5AC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -396,6 +396,14 @@
   </si>
   <si>
     <t>午睡，但是清醒梦，精力吃光光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有睡着，早上也睡不下去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸2 勺，瓜拉纳3勺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -710,6 +718,12 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="45">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -3630,7 +3644,9 @@
       <c r="E48" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="2"/>
+      <c r="H48" s="2">
+        <v>3</v>
+      </c>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
@@ -3646,16 +3662,22 @@
       <c r="A50" s="3">
         <v>46152</v>
       </c>
-      <c r="C50" s="2"/>
+      <c r="C50" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="D50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="E50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" s="2">
+        <v>3</v>
+      </c>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>46153</v>
       </c>
-      <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD52ECF-EB77-414A-B651-840CA0D5AC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFA106-6BCB-495B-AE74-9E05F6C2BA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -404,6 +404,18 @@
   </si>
   <si>
     <t>硫辛酸2 勺，瓜拉纳3勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡不下去，睡眠非常浅。但是今天意外的精神，没有服用药物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20分钟午觉，质量糟糕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓜拉纳1勺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -725,6 +737,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3678,8 +3693,18 @@
       <c r="A51" s="3">
         <v>46153</v>
       </c>
-      <c r="D51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H51" s="2">
+        <v>4</v>
+      </c>
       <c r="I51" s="2"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFA106-6BCB-495B-AE74-9E05F6C2BA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5D50B9-96D2-4A36-8566-E441564208C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="98">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,6 +416,18 @@
   </si>
   <si>
     <t>瓜拉纳1勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困倦，夜色失去了提神效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有午睡，我需要攒个睡眠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓜拉纳2勺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -740,6 +752,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3711,9 +3726,18 @@
       <c r="A52" s="3">
         <v>46154</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="H52" s="2"/>
+      <c r="C52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="2">
+        <v>3</v>
+      </c>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5D50B9-96D2-4A36-8566-E441564208C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBD6859-D3F3-4E56-B067-459D92869492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -428,6 +428,18 @@
   </si>
   <si>
     <t>瓜拉纳2勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>困倦，随着时间在增加，临近睡觉时候最大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫辛酸 1 勺，瓜拉纳1勺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提前关灯，大抵能睡得好些</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -755,6 +767,12 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3744,17 +3762,29 @@
       <c r="A53" s="3">
         <v>46155</v>
       </c>
-      <c r="C53" s="2"/>
+      <c r="C53" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="D53" s="2"/>
-      <c r="H53" s="2"/>
+      <c r="E53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H53" s="2">
+        <v>4</v>
+      </c>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>46156</v>
       </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
       <c r="D54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="H54" s="2">
+        <v>5</v>
+      </c>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBD6859-D3F3-4E56-B067-459D92869492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8752112C-9300-403D-8E4D-E82E4C3472A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17040" yWindow="870" windowWidth="11145" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,6 +440,14 @@
   </si>
   <si>
     <t>提前关灯，大抵能睡得好些</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡得非常香，早上时候还做了好多梦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶氨酸1g</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -773,6 +781,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3807,10 +3818,22 @@
       <c r="A58" s="3">
         <v>46160</v>
       </c>
+      <c r="C58" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>46161</v>
+      </c>
+      <c r="E59" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8752112C-9300-403D-8E4D-E82E4C3472A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D455370D-9F90-4F08-9F79-57831A42DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17040" yWindow="870" windowWidth="11145" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="104">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,10 @@
   </si>
   <si>
     <t>茶氨酸1g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶氨酸1g，瓜拉纳2勺，对乙酰氨基酚0.6g</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -525,18 +529,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,14 +541,53 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -784,6 +820,12 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2468,20 +2510,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:K100" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:K100" totalsRowShown="0" headerRowDxfId="12" dataDxfId="0">
   <autoFilter ref="A1:K100" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况"/>
-    <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）"/>
-    <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为"/>
-    <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物"/>
-    <tableColumn id="11" xr3:uid="{7B1284C1-BD4F-40C2-8A90-EA6374B9CCBF}" name="B"/>
-    <tableColumn id="12" xr3:uid="{4889870D-81B3-48E8-8B32-09DEA589C185}" name="C"/>
-    <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数"/>
-    <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例"/>
-    <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述"/>
-    <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他"/>
+    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{7B1284C1-BD4F-40C2-8A90-EA6374B9CCBF}" name="B" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{4889870D-81B3-48E8-8B32-09DEA589C185}" name="C" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2757,7 +2799,7 @@
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76" customWidth="1"/>
-    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.5" customWidth="1"/>
     <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="77.5" bestFit="1" customWidth="1"/>
@@ -2800,1303 +2842,1886 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="8">
         <v>46104</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
         <v>5</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="8">
         <v>46105</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
         <v>6</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="8">
         <v>46106</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>6</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="8">
         <v>46107</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
         <v>6</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="9" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="8">
         <v>46108</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>4</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="8">
         <v>46109</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
         <v>6</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="8">
         <v>46110</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5">
         <v>6</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="8">
         <v>46111</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
         <v>5</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="2"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="8">
         <v>46112</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
         <v>3</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="2"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="8">
         <v>46113</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="H11" s="2">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
         <v>6</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="2"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="8">
         <v>46114</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
         <v>7</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="8">
         <v>46115</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="2">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4">
         <v>7</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="8">
         <v>46116</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4">
         <v>7</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="8">
         <v>46117</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2">
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4">
         <v>8</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="8">
         <v>46118</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4">
         <v>5</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
         <v>46119</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
         <v>6</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
         <v>46120</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4">
         <v>5</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
         <v>46121</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2">
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4">
         <v>3</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
         <v>46122</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2">
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4">
         <v>3</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
         <v>46123</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4">
         <v>4</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
         <v>46124</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4">
         <v>4</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
         <v>46125</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2">
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4">
         <v>5</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
         <v>46126</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4">
         <v>4</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
         <v>46127</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2">
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4">
         <v>3</v>
       </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>46128</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4">
         <v>5</v>
       </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
         <v>46129</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>46130</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4">
         <v>6</v>
       </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
         <v>46131</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2">
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4">
         <v>6</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
         <v>46132</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4">
         <v>5</v>
       </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
         <v>46133</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4">
         <v>4</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
         <v>46134</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4">
         <v>3</v>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>46135</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2">
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4">
         <v>4</v>
       </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>46136</v>
       </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
         <v>46137</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4">
         <v>4</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
         <v>46138</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4">
         <v>6</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
         <v>46139</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="2">
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="4">
         <v>5</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
         <v>46140</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2">
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4">
         <v>4</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
         <v>46141</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2">
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4">
         <v>4</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
         <v>46142</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4">
         <v>3</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="8">
         <v>46143</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2" t="s">
+      <c r="D41" s="4"/>
+      <c r="E41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2">
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4">
         <v>4</v>
       </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="8">
         <v>46144</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2" t="s">
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="2">
+      <c r="F42" s="4"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="4">
         <v>5</v>
       </c>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
         <v>46145</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="H43" s="2">
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4">
         <v>6</v>
       </c>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
         <v>46146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="H44" s="2">
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4">
         <v>6</v>
       </c>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="8">
         <v>46147</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="H45" s="2">
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4">
         <v>6</v>
       </c>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="8">
         <v>46148</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2" t="s">
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="2">
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4">
         <v>4</v>
       </c>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="8">
         <v>46149</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="4"/>
+      <c r="E47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="2">
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4">
         <v>3</v>
       </c>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
         <v>46150</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="2">
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4">
         <v>3</v>
       </c>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
         <v>46151</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
         <v>46152</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H50" s="2">
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4">
         <v>3</v>
       </c>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
         <v>46153</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H51" s="2">
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4">
         <v>4</v>
       </c>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
         <v>46154</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H52" s="2">
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4">
         <v>3</v>
       </c>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
         <v>46155</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="4"/>
+      <c r="E53" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H53" s="2">
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4">
         <v>4</v>
       </c>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
         <v>46156</v>
       </c>
-      <c r="C54" t="s">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D54" s="2"/>
-      <c r="H54" s="2">
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4">
         <v>5</v>
       </c>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
         <v>46157</v>
       </c>
-      <c r="D55" s="2"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
         <v>46158</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
         <v>46159</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
         <v>46160</v>
       </c>
-      <c r="C58" t="s">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E58" t="s">
+      <c r="D58" s="4"/>
+      <c r="E58" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H58">
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
         <v>46161</v>
       </c>
-      <c r="E59" t="s">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4">
+        <v>5</v>
+      </c>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
         <v>46162</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4">
+        <v>4</v>
+      </c>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
         <v>46163</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
         <v>46164</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
         <v>46165</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
         <v>46166</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
         <v>46167</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
         <v>46168</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
         <v>46169</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
         <v>46170</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
         <v>46171</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
         <v>46172</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
         <v>46173</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
         <v>46174</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" s="8">
         <v>46175</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
         <v>46176</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
         <v>46177</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="8">
         <v>46178</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="8">
         <v>46179</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="8">
         <v>46180</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" s="8">
         <v>46181</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="8">
         <v>46182</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" s="8">
         <v>46183</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
         <v>46184</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" s="8">
         <v>46185</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" s="8">
         <v>46186</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="8">
         <v>46187</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="8">
         <v>46188</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="8">
         <v>46189</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="8">
         <v>46190</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="8">
         <v>46191</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="8">
         <v>46192</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="8">
         <v>46193</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
         <v>46194</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
         <v>46195</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
         <v>46196</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
         <v>46197</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
         <v>46198</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
         <v>46199</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
         <v>46200</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
         <v>46201</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
         <v>46202</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>46203</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>46204</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>46205</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>46206</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>46208</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>46209</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>46210</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>46211</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>46212</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>46213</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>46214</v>
       </c>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D455370D-9F90-4F08-9F79-57831A42DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59761D27-F57A-459F-AC0C-4FA653C9E5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -452,6 +452,14 @@
   </si>
   <si>
     <t>茶氨酸1g，瓜拉纳2勺，对乙酰氨基酚0.6g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上睡过头了，但设法清醒了一整天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我发现服用茶氨酸会导致提早起床，但是似乎不和这个相关</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -535,16 +543,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,10 +591,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -826,6 +834,12 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,20 +2524,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:K100" totalsRowShown="0" headerRowDxfId="12" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}" name="表2" displayName="表2" ref="A1:K100" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:K100" xr:uid="{1357AEC5-7810-46B0-9196-9A7A22533729}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{7B1284C1-BD4F-40C2-8A90-EA6374B9CCBF}" name="B" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{4889870D-81B3-48E8-8B32-09DEA589C185}" name="C" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{72CCD1AA-FD83-499C-8DF2-FFED0C588AE4}" name="时间" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{5F247579-35FF-411E-B37E-0FAC4B508905}" name="状况" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F3D96D49-245E-42B9-B777-06EE724BAFAA}" name="睡眠（昨晚）" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{ABCAD6CE-1668-43ED-9B93-7DB8186E0A1B}" name="行为" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{C235B3EF-762A-4F27-8CAA-848445531A93}" name="药物" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{7B1284C1-BD4F-40C2-8A90-EA6374B9CCBF}" name="B" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{4889870D-81B3-48E8-8B32-09DEA589C185}" name="C" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{2F2152C6-1616-4375-A900-1E99DA9C9CAB}" name="分数" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{630334AF-0C89-4BC5-8146-36F4C9265153}" name="不知名的病例" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{FB741644-F914-47F7-BF97-12406888E0F3}" name="病例描述" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{85402970-6FA6-4643-8DA5-57F3A40391ED}" name="其他" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2842,7 +2856,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>46104</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -2867,7 +2881,7 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <v>46105</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2892,7 +2906,7 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>46106</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -2919,7 +2933,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>46107</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2940,14 +2954,14 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>46108</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -2968,12 +2982,12 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>46109</v>
       </c>
       <c r="B7" s="5"/>
@@ -2992,12 +3006,12 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>46110</v>
       </c>
       <c r="B8" s="4"/>
@@ -3016,12 +3030,12 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>46111</v>
       </c>
       <c r="B9" s="4"/>
@@ -3042,7 +3056,7 @@
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>46112</v>
       </c>
       <c r="B10" s="4"/>
@@ -3065,7 +3079,7 @@
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>46113</v>
       </c>
       <c r="B11" s="4"/>
@@ -3084,7 +3098,7 @@
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>46114</v>
       </c>
       <c r="B12" s="4"/>
@@ -3103,7 +3117,7 @@
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>46115</v>
       </c>
       <c r="B13" s="4"/>
@@ -3126,7 +3140,7 @@
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>46116</v>
       </c>
       <c r="B14" s="4"/>
@@ -3149,7 +3163,7 @@
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
+      <c r="A15" s="6">
         <v>46117</v>
       </c>
       <c r="B15" s="4"/>
@@ -3172,7 +3186,7 @@
       <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>46118</v>
       </c>
       <c r="B16" s="4"/>
@@ -3195,7 +3209,7 @@
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>46119</v>
       </c>
       <c r="B17" s="4"/>
@@ -3214,7 +3228,7 @@
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>46120</v>
       </c>
       <c r="B18" s="4"/>
@@ -3235,7 +3249,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <v>46121</v>
       </c>
       <c r="B19" s="4"/>
@@ -3258,7 +3272,7 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
+      <c r="A20" s="6">
         <v>46122</v>
       </c>
       <c r="B20" s="4"/>
@@ -3279,7 +3293,7 @@
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>46123</v>
       </c>
       <c r="B21" s="4"/>
@@ -3298,7 +3312,7 @@
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <v>46124</v>
       </c>
       <c r="B22" s="4"/>
@@ -3317,7 +3331,7 @@
       <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
+      <c r="A23" s="6">
         <v>46125</v>
       </c>
       <c r="B23" s="4"/>
@@ -3338,7 +3352,7 @@
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
+      <c r="A24" s="6">
         <v>46126</v>
       </c>
       <c r="B24" s="4"/>
@@ -3359,7 +3373,7 @@
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
+      <c r="A25" s="6">
         <v>46127</v>
       </c>
       <c r="B25" s="4"/>
@@ -3380,7 +3394,7 @@
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="A26" s="6">
         <v>46128</v>
       </c>
       <c r="B26" s="4"/>
@@ -3401,7 +3415,7 @@
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="A27" s="6">
         <v>46129</v>
       </c>
       <c r="B27" s="4"/>
@@ -3416,7 +3430,7 @@
       <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
+      <c r="A28" s="6">
         <v>46130</v>
       </c>
       <c r="B28" s="4"/>
@@ -3435,7 +3449,7 @@
       <c r="K28" s="4"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+      <c r="A29" s="6">
         <v>46131</v>
       </c>
       <c r="B29" s="4"/>
@@ -3454,7 +3468,7 @@
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
+      <c r="A30" s="6">
         <v>46132</v>
       </c>
       <c r="B30" s="4"/>
@@ -3477,7 +3491,7 @@
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
+      <c r="A31" s="6">
         <v>46133</v>
       </c>
       <c r="B31" s="4"/>
@@ -3494,7 +3508,7 @@
       <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
+      <c r="A32" s="6">
         <v>46134</v>
       </c>
       <c r="B32" s="4"/>
@@ -3515,7 +3529,7 @@
       <c r="K32" s="4"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
+      <c r="A33" s="6">
         <v>46135</v>
       </c>
       <c r="B33" s="4"/>
@@ -3536,7 +3550,7 @@
       <c r="K33" s="4"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
+      <c r="A34" s="6">
         <v>46136</v>
       </c>
       <c r="B34" s="4"/>
@@ -3551,7 +3565,7 @@
       <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
+      <c r="A35" s="6">
         <v>46137</v>
       </c>
       <c r="B35" s="4"/>
@@ -3572,7 +3586,7 @@
       <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
+      <c r="A36" s="6">
         <v>46138</v>
       </c>
       <c r="B36" s="4"/>
@@ -3591,7 +3605,7 @@
       <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
+      <c r="A37" s="6">
         <v>46139</v>
       </c>
       <c r="B37" s="4"/>
@@ -3600,8 +3614,8 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
       <c r="H37" s="4">
         <v>5</v>
       </c>
@@ -3610,7 +3624,7 @@
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
+      <c r="A38" s="6">
         <v>46140</v>
       </c>
       <c r="B38" s="4"/>
@@ -3629,7 +3643,7 @@
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
+      <c r="A39" s="6">
         <v>46141</v>
       </c>
       <c r="B39" s="4"/>
@@ -3650,7 +3664,7 @@
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
+      <c r="A40" s="6">
         <v>46142</v>
       </c>
       <c r="B40" s="4"/>
@@ -3673,7 +3687,7 @@
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
+      <c r="A41" s="6">
         <v>46143</v>
       </c>
       <c r="B41" s="4"/>
@@ -3694,7 +3708,7 @@
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="8">
+      <c r="A42" s="6">
         <v>46144</v>
       </c>
       <c r="B42" s="4"/>
@@ -3706,7 +3720,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="9"/>
+      <c r="G42" s="7"/>
       <c r="H42" s="4">
         <v>5</v>
       </c>
@@ -3715,7 +3729,7 @@
       <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="8">
+      <c r="A43" s="6">
         <v>46145</v>
       </c>
       <c r="B43" s="4"/>
@@ -3734,7 +3748,7 @@
       <c r="K43" s="4"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="8">
+      <c r="A44" s="6">
         <v>46146</v>
       </c>
       <c r="B44" s="4"/>
@@ -3753,7 +3767,7 @@
       <c r="K44" s="4"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="8">
+      <c r="A45" s="6">
         <v>46147</v>
       </c>
       <c r="B45" s="4"/>
@@ -3772,7 +3786,7 @@
       <c r="K45" s="4"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="8">
+      <c r="A46" s="6">
         <v>46148</v>
       </c>
       <c r="B46" s="4"/>
@@ -3793,7 +3807,7 @@
       <c r="K46" s="4"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="8">
+      <c r="A47" s="6">
         <v>46149</v>
       </c>
       <c r="B47" s="4"/>
@@ -3814,7 +3828,7 @@
       <c r="K47" s="4"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="8">
+      <c r="A48" s="6">
         <v>46150</v>
       </c>
       <c r="B48" s="4"/>
@@ -3837,7 +3851,7 @@
       <c r="K48" s="4"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
+      <c r="A49" s="6">
         <v>46151</v>
       </c>
       <c r="B49" s="4"/>
@@ -3852,7 +3866,7 @@
       <c r="K49" s="4"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="8">
+      <c r="A50" s="6">
         <v>46152</v>
       </c>
       <c r="B50" s="4"/>
@@ -3873,7 +3887,7 @@
       <c r="K50" s="4"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="8">
+      <c r="A51" s="6">
         <v>46153</v>
       </c>
       <c r="B51" s="4"/>
@@ -3896,7 +3910,7 @@
       <c r="K51" s="4"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="8">
+      <c r="A52" s="6">
         <v>46154</v>
       </c>
       <c r="B52" s="4"/>
@@ -3919,7 +3933,7 @@
       <c r="K52" s="4"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="8">
+      <c r="A53" s="6">
         <v>46155</v>
       </c>
       <c r="B53" s="4"/>
@@ -3940,7 +3954,7 @@
       <c r="K53" s="4"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="8">
+      <c r="A54" s="6">
         <v>46156</v>
       </c>
       <c r="B54" s="4"/>
@@ -3959,7 +3973,7 @@
       <c r="K54" s="4"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="8">
+      <c r="A55" s="6">
         <v>46157</v>
       </c>
       <c r="B55" s="4"/>
@@ -3974,7 +3988,7 @@
       <c r="K55" s="4"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="8">
+      <c r="A56" s="6">
         <v>46158</v>
       </c>
       <c r="B56" s="4"/>
@@ -3989,7 +4003,7 @@
       <c r="K56" s="4"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="8">
+      <c r="A57" s="6">
         <v>46159</v>
       </c>
       <c r="B57" s="4"/>
@@ -4004,7 +4018,7 @@
       <c r="K57" s="4"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="8">
+      <c r="A58" s="6">
         <v>46160</v>
       </c>
       <c r="B58" s="4"/>
@@ -4025,7 +4039,7 @@
       <c r="K58" s="4"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="8">
+      <c r="A59" s="6">
         <v>46161</v>
       </c>
       <c r="B59" s="4"/>
@@ -4046,7 +4060,7 @@
       <c r="K59" s="4"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="8">
+      <c r="A60" s="6">
         <v>46162</v>
       </c>
       <c r="B60" s="4"/>
@@ -4067,7 +4081,7 @@
       <c r="K60" s="4"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="8">
+      <c r="A61" s="6">
         <v>46163</v>
       </c>
       <c r="B61" s="4"/>
@@ -4082,7 +4096,7 @@
       <c r="K61" s="4"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="8">
+      <c r="A62" s="6">
         <v>46164</v>
       </c>
       <c r="B62" s="4"/>
@@ -4097,7 +4111,7 @@
       <c r="K62" s="4"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="8">
+      <c r="A63" s="6">
         <v>46165</v>
       </c>
       <c r="B63" s="4"/>
@@ -4112,37 +4126,49 @@
       <c r="K63" s="4"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="8">
+      <c r="A64" s="6">
         <v>46166</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
+      <c r="C64" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="H64" s="4">
+        <v>5</v>
+      </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="8">
+      <c r="A65" s="6">
         <v>46167</v>
       </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
+      <c r="C65" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="H65" s="4">
+        <v>6</v>
+      </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="8">
+      <c r="A66" s="6">
         <v>46168</v>
       </c>
       <c r="B66" s="4"/>
@@ -4157,7 +4183,7 @@
       <c r="K66" s="4"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="8">
+      <c r="A67" s="6">
         <v>46169</v>
       </c>
       <c r="B67" s="4"/>
@@ -4172,7 +4198,7 @@
       <c r="K67" s="4"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="8">
+      <c r="A68" s="6">
         <v>46170</v>
       </c>
       <c r="B68" s="4"/>
@@ -4187,7 +4213,7 @@
       <c r="K68" s="4"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="8">
+      <c r="A69" s="6">
         <v>46171</v>
       </c>
       <c r="B69" s="4"/>
@@ -4202,7 +4228,7 @@
       <c r="K69" s="4"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="8">
+      <c r="A70" s="6">
         <v>46172</v>
       </c>
       <c r="B70" s="4"/>
@@ -4217,7 +4243,7 @@
       <c r="K70" s="4"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="8">
+      <c r="A71" s="6">
         <v>46173</v>
       </c>
       <c r="B71" s="4"/>
@@ -4232,7 +4258,7 @@
       <c r="K71" s="4"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="8">
+      <c r="A72" s="6">
         <v>46174</v>
       </c>
       <c r="B72" s="4"/>
@@ -4247,7 +4273,7 @@
       <c r="K72" s="4"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="8">
+      <c r="A73" s="6">
         <v>46175</v>
       </c>
       <c r="B73" s="4"/>
@@ -4262,7 +4288,7 @@
       <c r="K73" s="4"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="8">
+      <c r="A74" s="6">
         <v>46176</v>
       </c>
       <c r="B74" s="4"/>
@@ -4277,7 +4303,7 @@
       <c r="K74" s="4"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="8">
+      <c r="A75" s="6">
         <v>46177</v>
       </c>
       <c r="B75" s="4"/>
@@ -4292,7 +4318,7 @@
       <c r="K75" s="4"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="8">
+      <c r="A76" s="6">
         <v>46178</v>
       </c>
       <c r="B76" s="4"/>
@@ -4307,7 +4333,7 @@
       <c r="K76" s="4"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="8">
+      <c r="A77" s="6">
         <v>46179</v>
       </c>
       <c r="B77" s="4"/>
@@ -4322,7 +4348,7 @@
       <c r="K77" s="4"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="8">
+      <c r="A78" s="6">
         <v>46180</v>
       </c>
       <c r="B78" s="4"/>
@@ -4337,7 +4363,7 @@
       <c r="K78" s="4"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="8">
+      <c r="A79" s="6">
         <v>46181</v>
       </c>
       <c r="B79" s="4"/>
@@ -4352,7 +4378,7 @@
       <c r="K79" s="4"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="8">
+      <c r="A80" s="6">
         <v>46182</v>
       </c>
       <c r="B80" s="4"/>
@@ -4367,7 +4393,7 @@
       <c r="K80" s="4"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="8">
+      <c r="A81" s="6">
         <v>46183</v>
       </c>
       <c r="B81" s="4"/>
@@ -4382,7 +4408,7 @@
       <c r="K81" s="4"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="8">
+      <c r="A82" s="6">
         <v>46184</v>
       </c>
       <c r="B82" s="4"/>
@@ -4397,7 +4423,7 @@
       <c r="K82" s="4"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="8">
+      <c r="A83" s="6">
         <v>46185</v>
       </c>
       <c r="B83" s="4"/>
@@ -4412,7 +4438,7 @@
       <c r="K83" s="4"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="8">
+      <c r="A84" s="6">
         <v>46186</v>
       </c>
       <c r="B84" s="4"/>
@@ -4427,7 +4453,7 @@
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="8">
+      <c r="A85" s="6">
         <v>46187</v>
       </c>
       <c r="B85" s="4"/>
@@ -4442,7 +4468,7 @@
       <c r="K85" s="4"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="8">
+      <c r="A86" s="6">
         <v>46188</v>
       </c>
       <c r="B86" s="4"/>
@@ -4457,7 +4483,7 @@
       <c r="K86" s="4"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A87" s="8">
+      <c r="A87" s="6">
         <v>46189</v>
       </c>
       <c r="B87" s="4"/>
@@ -4472,7 +4498,7 @@
       <c r="K87" s="4"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="8">
+      <c r="A88" s="6">
         <v>46190</v>
       </c>
       <c r="B88" s="4"/>
@@ -4487,7 +4513,7 @@
       <c r="K88" s="4"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="8">
+      <c r="A89" s="6">
         <v>46191</v>
       </c>
       <c r="B89" s="4"/>
@@ -4502,7 +4528,7 @@
       <c r="K89" s="4"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="8">
+      <c r="A90" s="6">
         <v>46192</v>
       </c>
       <c r="B90" s="4"/>
@@ -4517,7 +4543,7 @@
       <c r="K90" s="4"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="8">
+      <c r="A91" s="6">
         <v>46193</v>
       </c>
       <c r="B91" s="4"/>
@@ -4532,7 +4558,7 @@
       <c r="K91" s="4"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="8">
+      <c r="A92" s="6">
         <v>46194</v>
       </c>
       <c r="B92" s="4"/>
@@ -4547,7 +4573,7 @@
       <c r="K92" s="4"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="8">
+      <c r="A93" s="6">
         <v>46195</v>
       </c>
       <c r="B93" s="4"/>
@@ -4562,7 +4588,7 @@
       <c r="K93" s="4"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="8">
+      <c r="A94" s="6">
         <v>46196</v>
       </c>
       <c r="B94" s="4"/>
@@ -4577,7 +4603,7 @@
       <c r="K94" s="4"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="8">
+      <c r="A95" s="6">
         <v>46197</v>
       </c>
       <c r="B95" s="4"/>
@@ -4592,7 +4618,7 @@
       <c r="K95" s="4"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="8">
+      <c r="A96" s="6">
         <v>46198</v>
       </c>
       <c r="B96" s="4"/>
@@ -4607,7 +4633,7 @@
       <c r="K96" s="4"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="8">
+      <c r="A97" s="6">
         <v>46199</v>
       </c>
       <c r="B97" s="4"/>
@@ -4622,7 +4648,7 @@
       <c r="K97" s="4"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="8">
+      <c r="A98" s="6">
         <v>46200</v>
       </c>
       <c r="B98" s="4"/>
@@ -4637,7 +4663,7 @@
       <c r="K98" s="4"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="8">
+      <c r="A99" s="6">
         <v>46201</v>
       </c>
       <c r="B99" s="4"/>
@@ -4652,7 +4678,7 @@
       <c r="K99" s="4"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="8">
+      <c r="A100" s="6">
         <v>46202</v>
       </c>
       <c r="B100" s="4"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59761D27-F57A-459F-AC0C-4FA653C9E5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B806019B-F9C3-4A6E-9B3A-E6B1D300FB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="108">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -460,6 +460,14 @@
   </si>
   <si>
     <t>我发现服用茶氨酸会导致提早起床，但是似乎不和这个相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清醒着的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午午睡，想象非常混乱且没有睡着</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4172,9 +4180,15 @@
         <v>46168</v>
       </c>
       <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
+      <c r="C66" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B806019B-F9C3-4A6E-9B3A-E6B1D300FB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7BA360-B8DA-4346-9274-6FC2CF0E82E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -468,6 +468,14 @@
   </si>
   <si>
     <t>中午午睡，想象非常混乱且没有睡着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午睡，但是脑子一直在运转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡死了，但是睡眠时间实在是太稀少了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4321,12 +4329,18 @@
         <v>46177</v>
       </c>
       <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
+      <c r="C75" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+      <c r="H75" s="4">
+        <v>2</v>
+      </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>

--- a/docs/表账/2026/2026健康检测.xlsx
+++ b/docs/表账/2026/2026健康检测.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7BA360-B8DA-4346-9274-6FC2CF0E82E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A122C4EE-F41F-4464-B0B6-1C7E15FD5375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="114">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -476,6 +476,22 @@
   </si>
   <si>
     <t>睡死了，但是睡眠时间实在是太稀少了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上被冻醒了，补充睡眠到11点，但是看起来质量不好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上提早醒了，设法继续睡觉，睡到9点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上没有睡着，早上时候做了些梦，是第三人称的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很晚睡觉，质量糟糕</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4355,7 +4371,9 @@
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="H76" s="4">
+        <v>3</v>
+      </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
@@ -4365,12 +4383,16 @@
         <v>46179</v>
       </c>
       <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="C77" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="H77" s="4">
+        <v>5</v>
+      </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
@@ -4380,12 +4402,16 @@
         <v>46180</v>
       </c>
       <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
+      <c r="C78" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
+      <c r="H78" s="4">
+        <v>4</v>
+      </c>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
@@ -4395,12 +4421,18 @@
         <v>46181</v>
       </c>
       <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
+      <c r="C79" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
+      <c r="H79" s="4">
+        <v>3</v>
+      </c>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -4410,12 +4442,18 @@
         <v>46182</v>
       </c>
       <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
+      <c r="C80" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
+      <c r="E80" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
+      <c r="H80" s="4">
+        <v>4</v>
+      </c>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
